--- a/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:19</t>
+    <t xml:space="preserve">2026-09-10 01:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:33</t>
+    <t xml:space="preserve">2026-09-12 22:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:45</t>
+    <t xml:space="preserve">2026-09-24 00:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:13</t>
+    <t xml:space="preserve">2026-10-02 15:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:57</t>
+    <t xml:space="preserve">2026-10-05 16:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
